--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.0.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.0.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
